--- a/output/Tables/2019/Monte Carlo/HIA_per_sex.xlsx
+++ b/output/Tables/2019/Monte Carlo/HIA_per_sex.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>24501.466</v>
+        <v>24489.621</v>
       </c>
       <c r="D2">
-        <v>22815.761</v>
+        <v>22819.909</v>
       </c>
       <c r="E2">
-        <v>26151.935</v>
+        <v>26161.992</v>
       </c>
       <c r="F2">
-        <v>286625.785</v>
+        <v>286604.404</v>
       </c>
       <c r="G2">
-        <v>275247.701</v>
+        <v>275336.177</v>
       </c>
       <c r="H2">
-        <v>297903.434</v>
+        <v>297913.657</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>38145221646.419</v>
+        <v>38119558461.711</v>
       </c>
       <c r="M2">
-        <v>36622738905.928</v>
+        <v>36611542033.456</v>
       </c>
       <c r="N2">
-        <v>39602385181.33</v>
+        <v>39622531159.505</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>34082.813</v>
+        <v>34001.953</v>
       </c>
       <c r="D3">
-        <v>31633.918</v>
+        <v>31531.574</v>
       </c>
       <c r="E3">
-        <v>36481.964</v>
+        <v>36467.359</v>
       </c>
       <c r="F3">
-        <v>318411.653</v>
+        <v>318208.5</v>
       </c>
       <c r="G3">
-        <v>302916.308</v>
+        <v>302482.139</v>
       </c>
       <c r="H3">
-        <v>334997.256</v>
+        <v>333896.654</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>42425855022.044</v>
+        <v>42316822520.455</v>
       </c>
       <c r="M3">
-        <v>40260711406.757</v>
+        <v>40226964651.033</v>
       </c>
       <c r="N3">
-        <v>44477807958.925</v>
+        <v>44426241931.395</v>
       </c>
     </row>
     <row r="4">
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>18838.682</v>
+        <v>18793.07</v>
       </c>
       <c r="D4">
-        <v>17772.288</v>
+        <v>17711.541</v>
       </c>
       <c r="E4">
-        <v>19904.139</v>
+        <v>19874.476</v>
       </c>
       <c r="F4">
-        <v>19092.621</v>
+        <v>19059.188</v>
       </c>
       <c r="G4">
-        <v>18173.586</v>
+        <v>18075.131</v>
       </c>
       <c r="H4">
-        <v>20104.145</v>
+        <v>20056.028</v>
       </c>
       <c r="I4">
-        <v>1048900281.887</v>
+        <v>1046738275.379</v>
       </c>
       <c r="J4">
-        <v>990652324.595</v>
+        <v>986326955.419</v>
       </c>
       <c r="K4">
-        <v>1112121965.608</v>
+        <v>1107829500.66</v>
       </c>
       <c r="L4">
-        <v>2536928606.133</v>
+        <v>2535356485.376</v>
       </c>
       <c r="M4">
-        <v>2408721112.171</v>
+        <v>2403895716.529</v>
       </c>
       <c r="N4">
-        <v>2664096207.17</v>
+        <v>2668530199.293</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>21343.115</v>
+        <v>21315.895</v>
       </c>
       <c r="D5">
-        <v>19780.512</v>
+        <v>19859.534</v>
       </c>
       <c r="E5">
-        <v>22801.946</v>
+        <v>22783.415</v>
       </c>
       <c r="F5">
-        <v>16845.125</v>
+        <v>16836.041</v>
       </c>
       <c r="G5">
-        <v>15805.175</v>
+        <v>15729.764</v>
       </c>
       <c r="H5">
-        <v>17989.622</v>
+        <v>17957.031</v>
       </c>
       <c r="I5">
-        <v>1186485813.309</v>
+        <v>1187311142.791</v>
       </c>
       <c r="J5">
-        <v>1106894051.331</v>
+        <v>1106090806.346</v>
       </c>
       <c r="K5">
-        <v>1266323320.719</v>
+        <v>1269593678.33</v>
       </c>
       <c r="L5">
-        <v>2240089797.983</v>
+        <v>2238768638.768</v>
       </c>
       <c r="M5">
-        <v>2096455522.738</v>
+        <v>2092284141.472</v>
       </c>
       <c r="N5">
-        <v>2385282351.618</v>
+        <v>2388281079.006</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>19966.669</v>
+        <v>20081.516</v>
       </c>
       <c r="D6">
-        <v>18819.269</v>
+        <v>18875.093</v>
       </c>
       <c r="E6">
-        <v>21158.775</v>
+        <v>21352.703</v>
       </c>
       <c r="F6">
-        <v>35649.279</v>
+        <v>36040.839</v>
       </c>
       <c r="G6">
-        <v>33232.543</v>
+        <v>33456.81</v>
       </c>
       <c r="H6">
-        <v>38232.672</v>
+        <v>38757.31</v>
       </c>
       <c r="I6">
-        <v>295640477.363</v>
+        <v>297373315.471</v>
       </c>
       <c r="J6">
-        <v>278341268.95</v>
+        <v>279411792.595</v>
       </c>
       <c r="K6">
-        <v>313271388.443</v>
+        <v>316068623.701</v>
       </c>
       <c r="L6">
-        <v>4743779558.439</v>
+        <v>4792039357.935</v>
       </c>
       <c r="M6">
-        <v>4426837553.204</v>
+        <v>4450798334.828</v>
       </c>
       <c r="N6">
-        <v>5073981091.098</v>
+        <v>5151628307.479</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>11035.363</v>
+        <v>11109.322</v>
       </c>
       <c r="D7">
-        <v>10170.747</v>
+        <v>10233.979</v>
       </c>
       <c r="E7">
-        <v>11990.031</v>
+        <v>12026.448</v>
       </c>
       <c r="F7">
-        <v>10922.769</v>
+        <v>10905.757</v>
       </c>
       <c r="G7">
-        <v>10044.827</v>
+        <v>10071.949</v>
       </c>
       <c r="H7">
-        <v>11732.86</v>
+        <v>11778.959</v>
       </c>
       <c r="I7">
-        <v>163546185.905</v>
+        <v>164511127.505</v>
       </c>
       <c r="J7">
-        <v>150351926.554</v>
+        <v>151570484.026</v>
       </c>
       <c r="K7">
-        <v>177913341.746</v>
+        <v>178050575.792</v>
       </c>
       <c r="L7">
-        <v>1452025090.843</v>
+        <v>1450638674.89</v>
       </c>
       <c r="M7">
-        <v>1344888266.954</v>
+        <v>1339509294.378</v>
       </c>
       <c r="N7">
-        <v>1567049951.587</v>
+        <v>1566345291.589</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>3023.994</v>
+        <v>3027.496</v>
       </c>
       <c r="D8">
-        <v>2827.507</v>
+        <v>2836.688</v>
       </c>
       <c r="E8">
-        <v>3220.825</v>
+        <v>3223.685</v>
       </c>
       <c r="F8">
-        <v>6385.212</v>
+        <v>6383.552</v>
       </c>
       <c r="G8">
-        <v>5978.767</v>
+        <v>5957.877</v>
       </c>
       <c r="H8">
-        <v>6788.226</v>
+        <v>6823.389</v>
       </c>
       <c r="I8">
-        <v>227438193.209</v>
+        <v>227632599.516</v>
       </c>
       <c r="J8">
-        <v>212859378.865</v>
+        <v>213256319.109</v>
       </c>
       <c r="K8">
-        <v>242697287.815</v>
+        <v>242458796.996</v>
       </c>
       <c r="L8">
-        <v>847059216.785</v>
+        <v>849085356.809</v>
       </c>
       <c r="M8">
-        <v>794058336.105</v>
+        <v>792748978.084</v>
       </c>
       <c r="N8">
-        <v>904873224.785</v>
+        <v>907379554.834</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>3372.537</v>
+        <v>3374.388</v>
       </c>
       <c r="D9">
-        <v>3115.013</v>
+        <v>3123.177</v>
       </c>
       <c r="E9">
-        <v>3623.25</v>
+        <v>3635.86</v>
       </c>
       <c r="F9">
-        <v>6128.074</v>
+        <v>6127.065</v>
       </c>
       <c r="G9">
-        <v>5597.972</v>
+        <v>5645.893</v>
       </c>
       <c r="H9">
-        <v>6611.991</v>
+        <v>6624.831</v>
       </c>
       <c r="I9">
-        <v>253852727.306</v>
+        <v>253735798.299</v>
       </c>
       <c r="J9">
-        <v>235009756.465</v>
+        <v>234796666.832</v>
       </c>
       <c r="K9">
-        <v>272265197.184</v>
+        <v>273327340.955</v>
       </c>
       <c r="L9">
-        <v>815612801.477</v>
+        <v>814833201.845</v>
       </c>
       <c r="M9">
-        <v>746687614.2690001</v>
+        <v>750997492.59</v>
       </c>
       <c r="N9">
-        <v>882125792.076</v>
+        <v>881024862.15</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>8489.784</v>
+        <v>8524.429</v>
       </c>
       <c r="D10">
-        <v>7844.663</v>
+        <v>7851.136</v>
       </c>
       <c r="E10">
-        <v>9198.362999999999</v>
+        <v>9198.151</v>
       </c>
       <c r="F10">
-        <v>16994.91</v>
+        <v>16975.802</v>
       </c>
       <c r="G10">
-        <v>15890.484</v>
+        <v>15911.601</v>
       </c>
       <c r="H10">
-        <v>18058.709</v>
+        <v>18066.435</v>
       </c>
       <c r="I10">
-        <v>143477919.529</v>
+        <v>143511784.616</v>
       </c>
       <c r="J10">
-        <v>131688593.465</v>
+        <v>132306014.615</v>
       </c>
       <c r="K10">
-        <v>154924929.985</v>
+        <v>154836783.018</v>
       </c>
       <c r="L10">
-        <v>2258926607.44</v>
+        <v>2258205329.733</v>
       </c>
       <c r="M10">
-        <v>2121747288.128</v>
+        <v>2116539468.081</v>
       </c>
       <c r="N10">
-        <v>2396018492.799</v>
+        <v>2402332595.172</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>5462.105</v>
+        <v>5410.258</v>
       </c>
       <c r="D11">
-        <v>4905.375</v>
+        <v>4873.393</v>
       </c>
       <c r="E11">
-        <v>5995.378</v>
+        <v>5962.759</v>
       </c>
       <c r="F11">
-        <v>6275.232</v>
+        <v>6261.378</v>
       </c>
       <c r="G11">
-        <v>5770.764</v>
+        <v>5765.817</v>
       </c>
       <c r="H11">
-        <v>6780.144</v>
+        <v>6763.014</v>
       </c>
       <c r="I11">
-        <v>91888606.234</v>
+        <v>91120322.031</v>
       </c>
       <c r="J11">
-        <v>82588224.236</v>
+        <v>82032962.007</v>
       </c>
       <c r="K11">
-        <v>101550703.813</v>
+        <v>100366907.395</v>
       </c>
       <c r="L11">
-        <v>833367434.553</v>
+        <v>832599266.104</v>
       </c>
       <c r="M11">
-        <v>769491934.258</v>
+        <v>766700706.527</v>
       </c>
       <c r="N11">
-        <v>899600646.701</v>
+        <v>899155680.4910001</v>
       </c>
     </row>
     <row r="12">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="C12">
-        <v>107144.622</v>
+        <v>107157.18</v>
       </c>
       <c r="D12">
-        <v>102075.199</v>
+        <v>101975.52</v>
       </c>
       <c r="E12">
-        <v>112577.42</v>
+        <v>112326.708</v>
       </c>
       <c r="F12">
-        <v>331285.046</v>
+        <v>12489.701</v>
       </c>
       <c r="G12">
-        <v>308326.158</v>
+        <v>11849.118</v>
       </c>
       <c r="H12">
-        <v>353546.031</v>
+        <v>13142.275</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -945,13 +945,13 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>44028816006.772</v>
+        <v>1661149862.992</v>
       </c>
       <c r="M12">
-        <v>41230768731.762</v>
+        <v>1575825839.458</v>
       </c>
       <c r="N12">
-        <v>47042811853.432</v>
+        <v>1747848875.106</v>
       </c>
     </row>
     <row r="13">
@@ -966,22 +966,22 @@
         </is>
       </c>
       <c r="C13">
-        <v>44779.056</v>
+        <v>44777.025</v>
       </c>
       <c r="D13">
-        <v>42270.893</v>
+        <v>42294.975</v>
       </c>
       <c r="E13">
-        <v>47328.53</v>
+        <v>47269.897</v>
       </c>
       <c r="F13">
-        <v>114415.384</v>
+        <v>5021.098</v>
       </c>
       <c r="G13">
-        <v>105996.215</v>
+        <v>4720.414</v>
       </c>
       <c r="H13">
-        <v>123360.287</v>
+        <v>5328.36</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>15266441475.213</v>
+        <v>667754010.4119999</v>
       </c>
       <c r="M13">
-        <v>14165007250.083</v>
+        <v>627688537.302</v>
       </c>
       <c r="N13">
-        <v>16392945161.596</v>
+        <v>708510896.7539999</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Monte Carlo/HIA_per_sex.xlsx
+++ b/output/Tables/2019/Monte Carlo/HIA_per_sex.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>24489.621</v>
+        <v>24484.449</v>
       </c>
       <c r="D2">
-        <v>22819.909</v>
+        <v>22817.462</v>
       </c>
       <c r="E2">
-        <v>26161.992</v>
+        <v>26152.374</v>
       </c>
       <c r="F2">
-        <v>286604.404</v>
+        <v>286576.089</v>
       </c>
       <c r="G2">
-        <v>275336.177</v>
+        <v>275338.354</v>
       </c>
       <c r="H2">
-        <v>297913.657</v>
+        <v>297893.073</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>38119558461.711</v>
+        <v>38116177736.526</v>
       </c>
       <c r="M2">
-        <v>36611542033.456</v>
+        <v>36611271347.41</v>
       </c>
       <c r="N2">
-        <v>39622531159.505</v>
+        <v>39614613576.173</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>34001.953</v>
+        <v>34004.503</v>
       </c>
       <c r="D3">
-        <v>31531.574</v>
+        <v>31528.612</v>
       </c>
       <c r="E3">
-        <v>36467.359</v>
+        <v>36463.26</v>
       </c>
       <c r="F3">
-        <v>318208.5</v>
+        <v>318196.098</v>
       </c>
       <c r="G3">
-        <v>302482.139</v>
+        <v>302440.325</v>
       </c>
       <c r="H3">
-        <v>333896.654</v>
+        <v>333928.733</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>42316822520.455</v>
+        <v>42316432594.079</v>
       </c>
       <c r="M3">
-        <v>40226964651.033</v>
+        <v>40223152023.432</v>
       </c>
       <c r="N3">
-        <v>44426241931.395</v>
+        <v>44430109220.601</v>
       </c>
     </row>
     <row r="4">
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>18793.07</v>
+        <v>18755.11</v>
       </c>
       <c r="D4">
-        <v>17711.541</v>
+        <v>17677.265</v>
       </c>
       <c r="E4">
-        <v>19874.476</v>
+        <v>19839.411</v>
       </c>
       <c r="F4">
-        <v>19059.188</v>
+        <v>19050.332</v>
       </c>
       <c r="G4">
-        <v>18075.131</v>
+        <v>18063.621</v>
       </c>
       <c r="H4">
-        <v>20056.028</v>
+        <v>20046.9</v>
       </c>
       <c r="I4">
-        <v>1046738275.379</v>
+        <v>1044651627.56</v>
       </c>
       <c r="J4">
-        <v>986326955.419</v>
+        <v>984478743.471</v>
       </c>
       <c r="K4">
-        <v>1107829500.66</v>
+        <v>1105798318.338</v>
       </c>
       <c r="L4">
-        <v>2535356485.376</v>
+        <v>2533963256.375</v>
       </c>
       <c r="M4">
-        <v>2403895716.529</v>
+        <v>2402329375.847</v>
       </c>
       <c r="N4">
-        <v>2668530199.293</v>
+        <v>2667165618.303</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>21315.895</v>
+        <v>21385.638</v>
       </c>
       <c r="D5">
-        <v>19859.534</v>
+        <v>19921.581</v>
       </c>
       <c r="E5">
-        <v>22783.415</v>
+        <v>22862.907</v>
       </c>
       <c r="F5">
-        <v>16836.041</v>
+        <v>16871.582</v>
       </c>
       <c r="G5">
-        <v>15729.764</v>
+        <v>15758.314</v>
       </c>
       <c r="H5">
-        <v>17957.031</v>
+        <v>18000.867</v>
       </c>
       <c r="I5">
-        <v>1187311142.791</v>
+        <v>1191126911.948</v>
       </c>
       <c r="J5">
-        <v>1106090806.346</v>
+        <v>1109578093.424</v>
       </c>
       <c r="K5">
-        <v>1269593678.33</v>
+        <v>1273622792.283</v>
       </c>
       <c r="L5">
-        <v>2238768638.768</v>
+        <v>2243857317.734</v>
       </c>
       <c r="M5">
-        <v>2092284141.472</v>
+        <v>2096703098.103</v>
       </c>
       <c r="N5">
-        <v>2388281079.006</v>
+        <v>2393290979.011</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>20081.516</v>
+        <v>20111.891</v>
       </c>
       <c r="D6">
-        <v>18875.093</v>
+        <v>18890.766</v>
       </c>
       <c r="E6">
-        <v>21352.703</v>
+        <v>21371.229</v>
       </c>
       <c r="F6">
-        <v>36040.839</v>
+        <v>36172.418</v>
       </c>
       <c r="G6">
-        <v>33456.81</v>
+        <v>33581.435</v>
       </c>
       <c r="H6">
-        <v>38757.31</v>
+        <v>38887.626</v>
       </c>
       <c r="I6">
-        <v>297373315.471</v>
+        <v>297819851.486</v>
       </c>
       <c r="J6">
-        <v>279411792.595</v>
+        <v>279728702.968</v>
       </c>
       <c r="K6">
-        <v>316068623.701</v>
+        <v>316572288.144</v>
       </c>
       <c r="L6">
-        <v>4792039357.935</v>
+        <v>4808911216.95</v>
       </c>
       <c r="M6">
-        <v>4450798334.828</v>
+        <v>4468372805.113</v>
       </c>
       <c r="N6">
-        <v>5151628307.479</v>
+        <v>5170465782.498</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>11109.322</v>
+        <v>11094.832</v>
       </c>
       <c r="D7">
-        <v>10233.979</v>
+        <v>10217.263</v>
       </c>
       <c r="E7">
-        <v>12026.448</v>
+        <v>12006.833</v>
       </c>
       <c r="F7">
-        <v>10905.757</v>
+        <v>10871.235</v>
       </c>
       <c r="G7">
-        <v>10071.949</v>
+        <v>10044.652</v>
       </c>
       <c r="H7">
-        <v>11778.959</v>
+        <v>11736</v>
       </c>
       <c r="I7">
-        <v>164511127.505</v>
+        <v>164272530.614</v>
       </c>
       <c r="J7">
-        <v>151570484.026</v>
+        <v>151323718.527</v>
       </c>
       <c r="K7">
-        <v>178050575.792</v>
+        <v>177764445.538</v>
       </c>
       <c r="L7">
-        <v>1450638674.89</v>
+        <v>1445940904.684</v>
       </c>
       <c r="M7">
-        <v>1339509294.378</v>
+        <v>1335700899.647</v>
       </c>
       <c r="N7">
-        <v>1566345291.589</v>
+        <v>1560893023.579</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>3027.496</v>
+        <v>3033.772</v>
       </c>
       <c r="D8">
-        <v>2836.688</v>
+        <v>2842.467</v>
       </c>
       <c r="E8">
-        <v>3223.685</v>
+        <v>3230.255</v>
       </c>
       <c r="F8">
-        <v>6383.552</v>
+        <v>6378.004</v>
       </c>
       <c r="G8">
-        <v>5957.877</v>
+        <v>5953.861</v>
       </c>
       <c r="H8">
-        <v>6823.389</v>
+        <v>6813.448</v>
       </c>
       <c r="I8">
-        <v>227632599.516</v>
+        <v>228123789.264</v>
       </c>
       <c r="J8">
-        <v>213256319.109</v>
+        <v>213702470.762</v>
       </c>
       <c r="K8">
-        <v>242458796.996</v>
+        <v>242980675.389</v>
       </c>
       <c r="L8">
-        <v>849085356.809</v>
+        <v>848347981.248</v>
       </c>
       <c r="M8">
-        <v>792748978.084</v>
+        <v>792288071.3710001</v>
       </c>
       <c r="N8">
-        <v>907379554.834</v>
+        <v>906109055.098</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>3374.388</v>
+        <v>3369.667</v>
       </c>
       <c r="D9">
-        <v>3123.177</v>
+        <v>3117.632</v>
       </c>
       <c r="E9">
-        <v>3635.86</v>
+        <v>3627.484</v>
       </c>
       <c r="F9">
-        <v>6127.065</v>
+        <v>6122.598</v>
       </c>
       <c r="G9">
-        <v>5645.893</v>
+        <v>5646.335</v>
       </c>
       <c r="H9">
-        <v>6624.831</v>
+        <v>6616.702</v>
       </c>
       <c r="I9">
-        <v>253735798.299</v>
+        <v>253383229.505</v>
       </c>
       <c r="J9">
-        <v>234796666.832</v>
+        <v>234404738.612</v>
       </c>
       <c r="K9">
-        <v>273327340.955</v>
+        <v>272910382.105</v>
       </c>
       <c r="L9">
-        <v>814833201.845</v>
+        <v>814148185.7410001</v>
       </c>
       <c r="M9">
-        <v>750997492.59</v>
+        <v>750956986.883</v>
       </c>
       <c r="N9">
-        <v>881024862.15</v>
+        <v>880323482.737</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>8524.429</v>
+        <v>8521.370000000001</v>
       </c>
       <c r="D10">
-        <v>7851.136</v>
+        <v>7849.49</v>
       </c>
       <c r="E10">
-        <v>9198.151</v>
+        <v>9194.843999999999</v>
       </c>
       <c r="F10">
-        <v>16975.802</v>
+        <v>16970.107</v>
       </c>
       <c r="G10">
-        <v>15911.601</v>
+        <v>15907.561</v>
       </c>
       <c r="H10">
-        <v>18066.435</v>
+        <v>18050.883</v>
       </c>
       <c r="I10">
-        <v>143511784.616</v>
+        <v>143464068.021</v>
       </c>
       <c r="J10">
-        <v>132306014.615</v>
+        <v>132237939.045</v>
       </c>
       <c r="K10">
-        <v>154836783.018</v>
+        <v>154774239.906</v>
       </c>
       <c r="L10">
-        <v>2258205329.733</v>
+        <v>2257486458.416</v>
       </c>
       <c r="M10">
-        <v>2116539468.081</v>
+        <v>2115441910.31</v>
       </c>
       <c r="N10">
-        <v>2402332595.172</v>
+        <v>2400254421.563</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>5410.258</v>
+        <v>5411.453</v>
       </c>
       <c r="D11">
-        <v>4873.393</v>
+        <v>4874.931</v>
       </c>
       <c r="E11">
-        <v>5962.759</v>
+        <v>5959.351</v>
       </c>
       <c r="F11">
-        <v>6261.378</v>
+        <v>6281.251</v>
       </c>
       <c r="G11">
-        <v>5765.817</v>
+        <v>5783.642</v>
       </c>
       <c r="H11">
-        <v>6763.014</v>
+        <v>6787.711</v>
       </c>
       <c r="I11">
-        <v>91120322.031</v>
+        <v>91142602.098</v>
       </c>
       <c r="J11">
-        <v>82032962.007</v>
+        <v>82086803.12899999</v>
       </c>
       <c r="K11">
-        <v>100366907.395</v>
+        <v>100350602.535</v>
       </c>
       <c r="L11">
-        <v>832599266.104</v>
+        <v>835375892.183</v>
       </c>
       <c r="M11">
-        <v>766700706.527</v>
+        <v>769269845.72</v>
       </c>
       <c r="N11">
-        <v>899155680.4910001</v>
+        <v>902383886.383</v>
       </c>
     </row>
     <row r="12">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="C12">
-        <v>107157.18</v>
+        <v>88819.649</v>
       </c>
       <c r="D12">
-        <v>101975.52</v>
+        <v>84397.554</v>
       </c>
       <c r="E12">
-        <v>112326.708</v>
+        <v>93304.664</v>
       </c>
       <c r="F12">
-        <v>12489.701</v>
+        <v>30395.587</v>
       </c>
       <c r="G12">
-        <v>11849.118</v>
+        <v>28403.745</v>
       </c>
       <c r="H12">
-        <v>13142.275</v>
+        <v>32470.677</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -945,13 +945,13 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>1661149862.992</v>
+        <v>4042315771.149</v>
       </c>
       <c r="M12">
-        <v>1575825839.458</v>
+        <v>3777336898.597</v>
       </c>
       <c r="N12">
-        <v>1747848875.106</v>
+        <v>4318768801.896</v>
       </c>
     </row>
     <row r="13">
@@ -966,22 +966,22 @@
         </is>
       </c>
       <c r="C13">
-        <v>44777.025</v>
+        <v>37145.571</v>
       </c>
       <c r="D13">
-        <v>42294.975</v>
+        <v>34994.476</v>
       </c>
       <c r="E13">
-        <v>47269.897</v>
+        <v>39306.954</v>
       </c>
       <c r="F13">
-        <v>5021.098</v>
+        <v>10611.26</v>
       </c>
       <c r="G13">
-        <v>4720.414</v>
+        <v>9808.359</v>
       </c>
       <c r="H13">
-        <v>5328.36</v>
+        <v>11445.969</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>667754010.4119999</v>
+        <v>1411022480.577</v>
       </c>
       <c r="M13">
-        <v>627688537.302</v>
+        <v>1304300582.914</v>
       </c>
       <c r="N13">
-        <v>708510896.7539999</v>
+        <v>1521190267.857</v>
       </c>
     </row>
   </sheetData>
